--- a/docs/Internship_artifacts/Defect_Tracker Template_v0.1.xlsx
+++ b/docs/Internship_artifacts/Defect_Tracker Template_v0.1.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve">Sl No</t>
   </si>
@@ -116,6 +116,12 @@
   </si>
   <si>
     <t>Jan-27-2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> add qudrent cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add cloude data base insted of local database</t>
   </si>
   <si>
     <t xml:space="preserve">User Interface</t>
@@ -131,7 +137,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
@@ -164,12 +170,6 @@
     </font>
     <font>
       <sz val="11.000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -218,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -237,10 +237,7 @@
     <xf fontId="5" fillId="0" borderId="1" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1028,20 +1025,34 @@
       </c>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" ht="14.25">
+    <row r="9" ht="28.5">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="5"/>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="I9" s="7"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="4"/>
+      <c r="J9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="L9" s="6"/>
     </row>
     <row r="10" ht="14.25">
@@ -1052,12 +1063,12 @@
       <c r="C10" s="5"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="8"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="8"/>
+      <c r="K10" s="5"/>
       <c r="L10" s="6"/>
     </row>
     <row r="11" ht="14.25">
@@ -1084,12 +1095,12 @@
       <c r="C12" s="5"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="8"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="8"/>
+      <c r="K12" s="5"/>
       <c r="L12" s="6"/>
     </row>
     <row r="13" ht="14.25">
@@ -1112,12 +1123,12 @@
       <c r="C14" s="5"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="8"/>
+      <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="8"/>
+      <c r="K14" s="5"/>
       <c r="L14" s="6"/>
     </row>
     <row r="15" ht="14.25">
@@ -1140,12 +1151,12 @@
       <c r="C16" s="5"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="8"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="8"/>
+      <c r="K16" s="5"/>
       <c r="L16" s="6"/>
     </row>
     <row r="17" ht="14.25">
@@ -1154,12 +1165,12 @@
       <c r="C17" s="5"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="8"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="8"/>
+      <c r="K17" s="5"/>
       <c r="L17" s="6"/>
     </row>
     <row r="18" ht="14.25">
@@ -1168,12 +1179,12 @@
       <c r="C18" s="5"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="8"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="8"/>
+      <c r="K18" s="5"/>
       <c r="L18" s="6"/>
     </row>
     <row r="19" ht="14.25">
@@ -1196,12 +1207,12 @@
       <c r="C20" s="5"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="8"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="8"/>
+      <c r="K20" s="5"/>
       <c r="L20" s="6"/>
     </row>
     <row r="21" ht="14.25">
@@ -1326,7 +1337,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1336,12 +1347,12 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="s">
-        <v>35</v>
+      <c r="A5" s="8" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Internship_artifacts/Defect_Tracker Template_v0.1.xlsx
+++ b/docs/Internship_artifacts/Defect_Tracker Template_v0.1.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Sl No</t>
   </si>
@@ -122,6 +122,15 @@
   </si>
   <si>
     <t xml:space="preserve">add cloude data base insted of local database</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deployed the application on the cloud platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> make appropriate changes and deploy app into cloud platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan- 7th and 8th - 2026</t>
   </si>
   <si>
     <t xml:space="preserve">User Interface</t>
@@ -137,6 +146,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yy"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <sz val="10.000000"/>
@@ -218,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -235,6 +247,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="1" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1059,16 +1074,32 @@
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="5"/>
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="L10" s="6"/>
     </row>
     <row r="11" ht="14.25">
@@ -1337,7 +1368,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -1347,12 +1378,12 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>37</v>
+      <c r="A5" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
